--- a/Action/Data/CSV/MobEnemy2/MobEnemyData.xlsx
+++ b/Action/Data/CSV/MobEnemy2/MobEnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action\Data\CSV\MobEnemy2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13150718-E90B-46D3-B633-D4CCCAF3E579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85B5EB20-B6CD-453A-ABED-29435ABCF43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -977,13 +977,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>0</v>
       </c>
@@ -1023,8 +1023,11 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1064,8 +1067,11 @@
         <f t="shared" ref="L2:L25" si="3">I2*20</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1105,8 +1111,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>0</v>
       </c>
@@ -1146,8 +1155,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1187,8 +1199,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>0</v>
       </c>
@@ -1228,8 +1243,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>0</v>
       </c>
@@ -1269,8 +1287,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>0</v>
       </c>
@@ -1310,8 +1331,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>0</v>
       </c>
@@ -1351,8 +1375,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>0</v>
       </c>
@@ -1392,8 +1419,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>0</v>
       </c>
@@ -1433,8 +1463,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>0</v>
       </c>
@@ -1474,8 +1507,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>0</v>
       </c>
@@ -1515,8 +1551,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>0</v>
       </c>
@@ -1556,8 +1595,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>0</v>
       </c>
@@ -1597,8 +1639,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>0</v>
       </c>
@@ -1638,8 +1683,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>0</v>
       </c>
@@ -1679,8 +1727,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>0</v>
       </c>
@@ -1720,8 +1771,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>0</v>
       </c>
@@ -1761,8 +1815,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>0</v>
       </c>
@@ -1802,8 +1859,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>0</v>
       </c>
@@ -1843,8 +1903,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>0</v>
       </c>
@@ -1884,8 +1947,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>0</v>
       </c>
@@ -1925,8 +1991,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>0</v>
       </c>
@@ -1966,8 +2035,11 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>0</v>
       </c>
@@ -2006,6 +2078,9 @@
       <c r="L25">
         <f t="shared" si="3"/>
         <v>20</v>
+      </c>
+      <c r="M25">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
